--- a/docs/data/jp/xlsx/4229.xlsx
+++ b/docs/data/jp/xlsx/4229.xlsx
@@ -9609,7 +9609,7 @@
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>Gain On Insurance Adjustment EI</t>
+          <t>보험 차익</t>
         </is>
       </c>
       <c r="I118" s="20" t="n">
@@ -14552,7 +14552,7 @@
     <row r="224">
       <c r="A224" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Treasury Stock Fin CF</t>
+          <t>자기주식 순증감액(△는 증가)</t>
         </is>
       </c>
       <c r="D224" s="20" t="n">
@@ -19229,7 +19229,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Provision For Assets Removal NCLLiabilities</t>
+          <t>고정자산 철거 충당금</t>
         </is>
       </c>
       <c r="C116" s="20" t="n">
@@ -19266,7 +19266,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Provision For Losses On Business Withdrawal NCL</t>
+          <t>사업 철수 손실 충당금</t>
         </is>
       </c>
       <c r="E117" s="20" t="n">
